--- a/results/Int Task Remove ACC 0.5/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.5/Linea_fi_explain.xlsx
@@ -1166,16 +1166,16 @@
         <v>0.04965895702659505</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009549696288749413</v>
+        <v>0.009548429373015508</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001483711941050969</v>
+        <v>0.0001530970920257013</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006481689923925775</v>
+        <v>0.006486375959539646</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007582786233406085</v>
+        <v>0.00757806702623289</v>
       </c>
       <c r="L3" t="n">
         <v>0.007573347819059698</v>
@@ -1184,7 +1184,7 @@
         <v>-0.002971468433873547</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02705261693867833</v>
+        <v>0.02704801500586655</v>
       </c>
       <c r="O3" t="n">
         <v>0.007233312281925493</v>
@@ -1196,7 +1196,7 @@
         <v>0.004158265294221438</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008322225240117756</v>
+        <v>0.008307546381905725</v>
       </c>
       <c r="S3" t="n">
         <v>0.3457320171943792</v>
@@ -1208,7 +1208,7 @@
         <v>0.2095272452927819</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001579001659930412</v>
+        <v>0.0001478477481936802</v>
       </c>
       <c r="W3" t="n">
         <v>0.005124783312880106</v>
@@ -1223,7 +1223,7 @@
         <v>0.005561673361253524</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03695545042023896</v>
+        <v>0.03696017631815956</v>
       </c>
       <c r="AB3" t="n">
         <v>7.271900098265061e-05</v>
@@ -1301,7 +1301,7 @@
         <v>0.02648014469838346</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.005328704219951585</v>
+        <v>0.00533343011787219</v>
       </c>
       <c r="BB3" t="n">
         <v>0.006651664115993899</v>
@@ -1319,7 +1319,7 @@
         <v>0.02735007964495349</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02029756412697304</v>
+        <v>0.02029234492029245</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0005065945566825115</v>
@@ -1385,7 +1385,7 @@
         <v>-0.0001485817072109852</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.005936643530565218</v>
+        <v>0.005931424323884634</v>
       </c>
       <c r="CD3" t="n">
         <v>0.001988478218154175</v>
@@ -1437,16 +1437,16 @@
         <v>0.05784651983911972</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02025792313418513</v>
+        <v>0.02024089088933098</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001184386991915831</v>
+        <v>0.001187799499991366</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02128474825430397</v>
+        <v>0.02128986165851083</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01644037023110092</v>
+        <v>0.01643472684069781</v>
       </c>
       <c r="L4" t="n">
         <v>0.01642909506757337</v>
@@ -1455,7 +1455,7 @@
         <v>0.01088419454176932</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02891538785375427</v>
+        <v>0.02892360836989155</v>
       </c>
       <c r="O4" t="n">
         <v>0.01983421385865218</v>
@@ -1467,7 +1467,7 @@
         <v>0.01850881393594566</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02075352828088601</v>
+        <v>0.02073080170273207</v>
       </c>
       <c r="S4" t="n">
         <v>0.143369821983315</v>
@@ -1479,7 +1479,7 @@
         <v>0.1045331802949445</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001199879564500531</v>
+        <v>0.001194063818548174</v>
       </c>
       <c r="W4" t="n">
         <v>0.01746424516869425</v>
@@ -1494,7 +1494,7 @@
         <v>0.01980255353763579</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0617118065525252</v>
+        <v>0.06171165966789326</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0005425870968911449</v>
@@ -1572,7 +1572,7 @@
         <v>0.03647767524260979</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.02097120129176039</v>
+        <v>0.02096103047773082</v>
       </c>
       <c r="BB4" t="n">
         <v>0.0252650666096798</v>
@@ -1590,7 +1590,7 @@
         <v>0.03742175034579841</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03928291228806444</v>
+        <v>0.0392880768885351</v>
       </c>
       <c r="BH4" t="n">
         <v>0.001410824581203901</v>
@@ -1656,7 +1656,7 @@
         <v>0.0008271890736327018</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01005349932946389</v>
+        <v>0.01003844108843336</v>
       </c>
       <c r="CD4" t="n">
         <v>0.005092733751717965</v>
@@ -1726,7 +1726,7 @@
         <v>-0.01632751937984488</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01942015646571559</v>
+        <v>-0.0194661757938334</v>
       </c>
       <c r="O5" t="n">
         <v>-0.01257750221434898</v>
@@ -1843,7 +1843,7 @@
         <v>-0.004647952139898726</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.03530245746691876</v>
+        <v>-0.03525519848771271</v>
       </c>
       <c r="BB5" t="n">
         <v>-0.03000945179584125</v>
@@ -1979,7 +1979,7 @@
         <v>-0.00480023118476466</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.007423733701361557</v>
+        <v>-0.007390518466640569</v>
       </c>
       <c r="I6" t="n">
         <v>-0.0004540147292175694</v>
@@ -2521,7 +2521,7 @@
         <v>0.09951775368994928</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01523944322476024</v>
+        <v>0.01525145090967859</v>
       </c>
       <c r="I8" t="n">
         <v>0.0003934653531629167</v>
@@ -2578,7 +2578,7 @@
         <v>0.003416891195089109</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05076884366675204</v>
+        <v>0.05078065841155355</v>
       </c>
       <c r="AB8" t="n">
         <v>0.000507303646160484</v>
@@ -2822,7 +2822,7 @@
         <v>0.03256484149855913</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04540311173974544</v>
+        <v>0.04530881659594534</v>
       </c>
       <c r="S9" t="n">
         <v>0.60398313027179</v>
@@ -2834,7 +2834,7 @@
         <v>0.3618216139688532</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002881844380403509</v>
+        <v>0.00283381364073011</v>
       </c>
       <c r="W9" t="n">
         <v>0.03279773156899808</v>
@@ -3011,7 +3011,7 @@
         <v>0.001207349081364872</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.03204592901878919</v>
+        <v>0.03199373695198334</v>
       </c>
       <c r="CD9" t="n">
         <v>0.01346555323590816</v>
